--- a/03_Group_comparisons/Proteome_training/c_data/03_set_contrasts.xlsx
+++ b/03_Group_comparisons/Proteome_training/c_data/03_set_contrasts.xlsx
@@ -4142,7 +4142,7 @@
     <t>03_Group_comparisons/Proteome_training/c_data/02_fit.rds</t>
   </si>
   <si>
-    <t>aacf5e18d593ba8d0ecb1981394483bd</t>
+    <t>04d8efdfac7c841cee0821c6e538de4d</t>
   </si>
   <si>
     <t>design</t>
@@ -4151,13 +4151,13 @@
     <t>03_Group_comparisons/Proteome_training/c_data/01_design.rds</t>
   </si>
   <si>
-    <t>614bbdf4f0c26542c91ed8556721be1c</t>
+    <t>2c8d64ee913e6b87df3bb15545693a35</t>
   </si>
   <si>
     <t>01_Processing/03_Quantification/c_data/DAList_limpa.rds</t>
   </si>
   <si>
-    <t>268362b9975bc00d3bc3b85b0f5736f7</t>
+    <t>015331bb453caea36bcabbe182b7eac6</t>
   </si>
   <si>
     <t>singscore</t>
@@ -4175,7 +4175,7 @@
     <t>00_Setup/Input/phenotype.csv</t>
   </si>
   <si>
-    <t>5a1989db406daa0b70189a9f0df52cf3</t>
+    <t>cdb8d908fb24ab0d2be6f2d00021db81</t>
   </si>
   <si>
     <t>BiocGenerics</t>
